--- a/data/memories/memory_01/assets/documents/hr/Employee Registry v2.xlsx
+++ b/data/memories/memory_01/assets/documents/hr/Employee Registry v2.xlsx
@@ -583,7 +583,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Laura C.</t>
+          <t>Laura L.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
